--- a/rules/CORE-000257/negative/02/data/unit-test-coreid-CG0061-negative 2.xlsx
+++ b/rules/CORE-000257/negative/02/data/unit-test-coreid-CG0061-negative 2.xlsx
@@ -35,7 +35,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor theme="0" tint="-0.1499984740745262"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +128,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +605,465 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HOSTRTPT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ho.xpt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HOSTTPT</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1477,12 @@
           <t>356</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="O5" s="8" t="n"/>
+      <c r="O5" s="10" t="n"/>
       <c r="P5" s="8" t="n"/>
       <c r="Q5" s="8" t="n"/>
     </row>
@@ -1083,11 +1552,12 @@
           <t>112</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>AFTER</t>
         </is>
       </c>
+      <c r="O6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1155,12 +1625,12 @@
           <t>1041</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="O7" s="8" t="n"/>
+      <c r="O7" s="10" t="n"/>
       <c r="P7" s="8" t="n"/>
       <c r="Q7" s="8" t="n"/>
     </row>
@@ -1230,11 +1700,12 @@
           <t>853</t>
         </is>
       </c>
-      <c r="N8" s="9" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
+      <c r="O8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1302,12 +1773,12 @@
           <t>847</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="O9" s="8" t="n"/>
+      <c r="O9" s="10" t="n"/>
       <c r="P9" s="8" t="n"/>
       <c r="Q9" s="8" t="n"/>
     </row>
@@ -1377,11 +1848,12 @@
           <t>576</t>
         </is>
       </c>
-      <c r="N10" s="9" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>AFTER</t>
         </is>
       </c>
+      <c r="O10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1449,12 +1921,12 @@
           <t>131</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="O11" s="8" t="n"/>
+      <c r="O11" s="10" t="n"/>
       <c r="P11" s="8" t="n"/>
       <c r="Q11" s="8" t="n"/>
     </row>
@@ -1524,11 +1996,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
+      <c r="O12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1596,12 +2069,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="O13" s="8" t="n"/>
+      <c r="O13" s="10" t="n"/>
       <c r="P13" s="8" t="n"/>
       <c r="Q13" s="8" t="n"/>
     </row>
